--- a/database.xlsx
+++ b/database.xlsx
@@ -5,26 +5,29 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://itdurangoedu-my.sharepoint.com/personal/alejandro_calderon_itdurango_edu_mx/Documents/Actualizacion docente/2025/index Y database para Gihub VALIDACION 2025/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/irione/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="9" documentId="13_ncr:1_{346A6530-4B93-A14A-9CF5-F682FC0EFE5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0C05F10D-8519-FD42-A6D6-C0D5F579348F}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D8D98FC-A325-2645-A3FC-B4C0A8708C52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="880" yWindow="540" windowWidth="33880" windowHeight="19380" activeTab="2" xr2:uid="{6728D57D-078C-EB4A-903D-70A501F530A6}"/>
+    <workbookView xWindow="11720" yWindow="600" windowWidth="23040" windowHeight="19380" xr2:uid="{6728D57D-078C-EB4A-903D-70A501F530A6}"/>
   </bookViews>
   <sheets>
-    <sheet name="Enero" sheetId="4" r:id="rId1"/>
-    <sheet name="Junio" sheetId="3" r:id="rId2"/>
-    <sheet name="Agosto" sheetId="5" r:id="rId3"/>
+    <sheet name="Enero 26" sheetId="7" r:id="rId1"/>
+    <sheet name="Enero" sheetId="4" r:id="rId2"/>
+    <sheet name="Junio" sheetId="3" r:id="rId3"/>
+    <sheet name="Agosto" sheetId="5" r:id="rId4"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId4"/>
+    <externalReference r:id="rId5"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Enero!$C$1:$C$423</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Enero!$C$1:$C$423</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Enero 26'!$C$1:$C$1</definedName>
+    <definedName name="EDUCACION_A_DISTANCIA" localSheetId="3">'[1]BD DOCENTES'!#REF!</definedName>
+    <definedName name="EDUCACION_A_DISTANCIA" localSheetId="1">#REF!</definedName>
+    <definedName name="EDUCACION_A_DISTANCIA" localSheetId="0">#REF!</definedName>
     <definedName name="EDUCACION_A_DISTANCIA" localSheetId="2">'[1]BD DOCENTES'!#REF!</definedName>
-    <definedName name="EDUCACION_A_DISTANCIA" localSheetId="0">#REF!</definedName>
-    <definedName name="EDUCACION_A_DISTANCIA" localSheetId="1">'[1]BD DOCENTES'!#REF!</definedName>
     <definedName name="EDUCACION_A_DISTANCIA">#REF!</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -48,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9002" uniqueCount="1982">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9226" uniqueCount="2057">
   <si>
     <t>GILDA FERNÁNDEZ VÁZQUEZ</t>
   </si>
@@ -6000,13 +6003,238 @@
   </si>
   <si>
     <t>TNM-054-93-2025-17</t>
+  </si>
+  <si>
+    <t>TNM-054-01-2026</t>
+  </si>
+  <si>
+    <t>TNM-054-02-2026</t>
+  </si>
+  <si>
+    <t>TNM-054-03-2026</t>
+  </si>
+  <si>
+    <t>TNM-054-04-2026</t>
+  </si>
+  <si>
+    <t>TNM-054-05-2026</t>
+  </si>
+  <si>
+    <t>TNM-054-06-2026</t>
+  </si>
+  <si>
+    <t>TNM-054-07-2026</t>
+  </si>
+  <si>
+    <t>TNM-054-08-2026</t>
+  </si>
+  <si>
+    <t>TNM-054-09-2026</t>
+  </si>
+  <si>
+    <t>TNM-054-10-2026</t>
+  </si>
+  <si>
+    <t>TNM-054-11-2026</t>
+  </si>
+  <si>
+    <t>TNM-054-12-2026</t>
+  </si>
+  <si>
+    <t>TNM-054-13-2026</t>
+  </si>
+  <si>
+    <t>TNM-054-14-2026</t>
+  </si>
+  <si>
+    <t>TNM-054-15-2026</t>
+  </si>
+  <si>
+    <t>TNM-054-16-2026</t>
+  </si>
+  <si>
+    <t>TNM-054-17-2026</t>
+  </si>
+  <si>
+    <t>TNM-054-18-2026</t>
+  </si>
+  <si>
+    <t>TNM-054-19-2026</t>
+  </si>
+  <si>
+    <t>TNM-054-20-2026-I</t>
+  </si>
+  <si>
+    <t>TNM-054-20-2026-II</t>
+  </si>
+  <si>
+    <t>TNM-054-20-2026-III</t>
+  </si>
+  <si>
+    <t>TNM-054-20-2026-IV</t>
+  </si>
+  <si>
+    <t>TNM-054-20-2026-V</t>
+  </si>
+  <si>
+    <t>TNM-054-20-2026-VI</t>
+  </si>
+  <si>
+    <t>TNM-054-20-2026-VII</t>
+  </si>
+  <si>
+    <t>TNM-054-20-2026-VIII</t>
+  </si>
+  <si>
+    <t>TNM-054-21-2026</t>
+  </si>
+  <si>
+    <t>TNM-054-23-2026</t>
+  </si>
+  <si>
+    <t>TNM-054-24-2026</t>
+  </si>
+  <si>
+    <t>TNM-054-22-2026</t>
+  </si>
+  <si>
+    <t>HÉCTOR GERARDO RODRIGUEZ GANDARA</t>
+  </si>
+  <si>
+    <t>PEDRO ANTONIO VELAZQUEZ VENTURA</t>
+  </si>
+  <si>
+    <t>IVÁN GONZÁLES LAZALDE</t>
+  </si>
+  <si>
+    <t>MARIA LUISA ORTIZ PARGA</t>
+  </si>
+  <si>
+    <t>PAULA FERNANDA HERNÁNDEZ AVITIA</t>
+  </si>
+  <si>
+    <t>AARÓN CUAUHTEMOC VARGAS FIERRO</t>
+  </si>
+  <si>
+    <t>PSIC. FABIOLA GONZÁLEZ CÁRDENAS</t>
+  </si>
+  <si>
+    <t>PSIC. OMAR ISRAEL RODRÍGUEZ RAMÍREZ</t>
+  </si>
+  <si>
+    <t>PSIC. MANUEL DE JESÚS CASTAÑEDA VÁZQUEZ</t>
+  </si>
+  <si>
+    <t>PSIC. DANIELA DE LA CRUZ HARO</t>
+  </si>
+  <si>
+    <t>L.N. CARLO ANTUAN CARRILLO CABRERA</t>
+  </si>
+  <si>
+    <t>PSIC. DENISSE UNZUETA VARGAS</t>
+  </si>
+  <si>
+    <t>PSIC. FRANCISCO PORRAS PARRAL</t>
+  </si>
+  <si>
+    <t>PST. ANDREA GARCIA DEL PALACIO</t>
+  </si>
+  <si>
+    <t>CELIDA CÓRDOVA NAVARRO</t>
+  </si>
+  <si>
+    <t>OPERACIÓN DEL LABORATORIO DE FÍSICA Y USO DEL MANUAL DE PRÁCTICAS</t>
+  </si>
+  <si>
+    <t>SISTEMAS DE REFRIGERACIÓN INDUSTRIAL</t>
+  </si>
+  <si>
+    <t>RESPUESTA METODOLÓGICA PARA EL CORRECTO LLENADO DE CEDULAS PARA LA ACREDITACIÓN DE LA CARRERA DE INGENIERÍA QUÍMICA</t>
+  </si>
+  <si>
+    <t>ANÁLISIS Y RESPUESTAS A LA CERTIFICACION CIEES ING. ELECTRICA</t>
+  </si>
+  <si>
+    <t>APERTURA DE TRABAJOS PARA REVISIÓN DE CIEES 2026 ING ELECTRONICA</t>
+  </si>
+  <si>
+    <t>HERRAMIENTAS DE INTELIGENCIA ARTIFICIAL PARA DOCENTES</t>
+  </si>
+  <si>
+    <t>INTRODUCCIÓN A LA CIENCIA DE DATOS</t>
+  </si>
+  <si>
+    <t>ELABORACIÓN DE HERRAMIENTAS PARA APOYO Y CONTROL EN LA IMPARTICIÓN DE CURSOS.</t>
+  </si>
+  <si>
+    <t>INTEGRACIÓN DE HERRAMIENTAS DIGITALES EN EL PROCESO DE DISEÑO, SKETCHUP-D5 RENDER- RERENDER AI</t>
+  </si>
+  <si>
+    <t>INTERFASE AUTOCAD-FACTORY CAD-FACTORY FLOW</t>
+  </si>
+  <si>
+    <t>AUTOMATIZACIÓN DE PROCESOS INDUSTRIALES</t>
+  </si>
+  <si>
+    <t>SIMULACIÓN CON PROMODELL</t>
+  </si>
+  <si>
+    <t>GESTIÓN DEL PROCESO ACADÉMICO PARA LA INTEGRACIÓN DE EXPEDIENTES ACADÉMICOS DE LOS DOCENTES DEL DEPARTAMENTO DE SISTEMAS Y COMPUTACIÓN</t>
+  </si>
+  <si>
+    <t>INTRODUCCIÓN A LA ENERGÍA FOTOVOLTAICA, CONCEPTOS Y APLICACIONES</t>
+  </si>
+  <si>
+    <t>CURSO PARA PRINCIPIANTES DE SOLIDWORK´S</t>
+  </si>
+  <si>
+    <t>APLICACIONES DEL MATHCAD EN EL DISEÑO DE ELEMENTOS DE CONCRETO REFORZADO CONFORME AL ACI 318-19.</t>
+  </si>
+  <si>
+    <t>BIM APLICADO AL DISEÑO ARQUITECTÓNICO CON REVIT</t>
+  </si>
+  <si>
+    <t>DISEÑO Y ELABORACIÓN DE INSTRUMENTACIÓN DIDÁCTICA ASISTIDA POR INTELIGENCIA ARTIFICIAL PARA LA IMPARTICIÓN EFICAZ DE CLASES</t>
+  </si>
+  <si>
+    <t>DOCENTES QUE SOSTIENEN: CUIDADO EMOCIONAL DEL ESTUDIANTE Y DEL DOCENTE</t>
+  </si>
+  <si>
+    <t>ELABORACIÓN DE INSTRUMENTACIÓN DIDÁCTICA COLEGIADA</t>
+  </si>
+  <si>
+    <t>DISEÑO DE INSTRUMENTOS DE EVALUACIÓN PARA LA IMPLEMENTACIÓN DE TECNOLOGÍAS DE INFORMACIÓN CON BASE EN EL NUEVO MODELO EDUCATIVO DEL TECNM --DIRIGIDO AL PERSONAL DE SISTEMAS Y COMPUTACIÓN--</t>
+  </si>
+  <si>
+    <t>TALLER DE DESARROLLO Y ELABORACION DE PRODUCTOS DE INVESTIGACION I</t>
+  </si>
+  <si>
+    <t>RESPUESTA METODOLÓGICA PARA EL CORRECTO LLENADO DE CEDULAS PARA LA ACREDITACIÓN DE LA CARRERA DE INGENIERÍA QUÍMICA PARTE II</t>
+  </si>
+  <si>
+    <t>DEPARTAMENTO DE CIENCIAS ECONÓMICO-ADMINISTRATIVAS</t>
+  </si>
+  <si>
+    <t>DEL 19 AL 23 DE ENERO DEL 2026</t>
+  </si>
+  <si>
+    <t>DEL 26 AL 30 DE ENERO DEL 2026</t>
+  </si>
+  <si>
+    <t>30 Horas</t>
+  </si>
+  <si>
+    <t>PROFESIONAL</t>
+  </si>
+  <si>
+    <t>DOCENTE</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -6100,6 +6328,18 @@
     <font>
       <sz val="10"/>
       <color rgb="FF1A1C1E"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -6463,7 +6703,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="93">
+  <cellXfs count="92">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -6639,11 +6879,8 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -7237,7 +7474,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -7552,6 +7789,761 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5BF5F7F8-EACA-E940-AF93-3C6EAFBACB07}">
+  <dimension ref="A1:G32"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="18" customWidth="1"/>
+    <col min="2" max="2" width="34.5" customWidth="1"/>
+    <col min="3" max="3" width="53.5" customWidth="1"/>
+    <col min="4" max="4" width="37.83203125" customWidth="1"/>
+    <col min="5" max="5" width="31.83203125" customWidth="1"/>
+    <col min="7" max="7" width="15.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" s="19" customFormat="1" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="89" t="s">
+        <v>1428</v>
+      </c>
+      <c r="B1" s="89" t="s">
+        <v>1429</v>
+      </c>
+      <c r="C1" s="89" t="s">
+        <v>1430</v>
+      </c>
+      <c r="D1" s="89" t="s">
+        <v>1431</v>
+      </c>
+      <c r="E1" s="89" t="s">
+        <v>1432</v>
+      </c>
+      <c r="F1" s="89" t="s">
+        <v>1433</v>
+      </c>
+      <c r="G1" s="89" t="s">
+        <v>1879</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="90" t="s">
+        <v>1982</v>
+      </c>
+      <c r="B2" s="90" t="s">
+        <v>33</v>
+      </c>
+      <c r="C2" s="91" t="s">
+        <v>2028</v>
+      </c>
+      <c r="D2" s="90" t="s">
+        <v>904</v>
+      </c>
+      <c r="E2" s="90" t="s">
+        <v>2052</v>
+      </c>
+      <c r="F2" s="90" t="s">
+        <v>2054</v>
+      </c>
+      <c r="G2" s="90" t="s">
+        <v>2055</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="90" t="s">
+        <v>1983</v>
+      </c>
+      <c r="B3" s="90" t="s">
+        <v>319</v>
+      </c>
+      <c r="C3" s="91" t="s">
+        <v>2029</v>
+      </c>
+      <c r="D3" s="90" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" s="90" t="s">
+        <v>2052</v>
+      </c>
+      <c r="F3" s="90" t="s">
+        <v>2054</v>
+      </c>
+      <c r="G3" s="90" t="s">
+        <v>2055</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="90" t="s">
+        <v>1984</v>
+      </c>
+      <c r="B4" s="90" t="s">
+        <v>2013</v>
+      </c>
+      <c r="C4" s="91" t="s">
+        <v>2030</v>
+      </c>
+      <c r="D4" s="90" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" s="90" t="s">
+        <v>2052</v>
+      </c>
+      <c r="F4" s="90" t="s">
+        <v>2054</v>
+      </c>
+      <c r="G4" s="90" t="s">
+        <v>2055</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="90" t="s">
+        <v>1985</v>
+      </c>
+      <c r="B5" s="90" t="s">
+        <v>1262</v>
+      </c>
+      <c r="C5" s="91" t="s">
+        <v>2031</v>
+      </c>
+      <c r="D5" s="90" t="s">
+        <v>7</v>
+      </c>
+      <c r="E5" s="90" t="s">
+        <v>2052</v>
+      </c>
+      <c r="F5" s="90" t="s">
+        <v>2054</v>
+      </c>
+      <c r="G5" s="90" t="s">
+        <v>2055</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="90" t="s">
+        <v>1986</v>
+      </c>
+      <c r="B6" s="90" t="s">
+        <v>2014</v>
+      </c>
+      <c r="C6" s="91" t="s">
+        <v>2032</v>
+      </c>
+      <c r="D6" s="90" t="s">
+        <v>7</v>
+      </c>
+      <c r="E6" s="90" t="s">
+        <v>2052</v>
+      </c>
+      <c r="F6" s="90" t="s">
+        <v>2054</v>
+      </c>
+      <c r="G6" s="90" t="s">
+        <v>2055</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="90" t="s">
+        <v>1987</v>
+      </c>
+      <c r="B7" s="90" t="s">
+        <v>850</v>
+      </c>
+      <c r="C7" s="91" t="s">
+        <v>2033</v>
+      </c>
+      <c r="D7" s="90" t="s">
+        <v>10</v>
+      </c>
+      <c r="E7" s="90" t="s">
+        <v>2052</v>
+      </c>
+      <c r="F7" s="90" t="s">
+        <v>2054</v>
+      </c>
+      <c r="G7" s="90" t="s">
+        <v>2055</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="90" t="s">
+        <v>1988</v>
+      </c>
+      <c r="B8" s="90" t="s">
+        <v>156</v>
+      </c>
+      <c r="C8" s="91" t="s">
+        <v>2034</v>
+      </c>
+      <c r="D8" s="90" t="s">
+        <v>866</v>
+      </c>
+      <c r="E8" s="90" t="s">
+        <v>2052</v>
+      </c>
+      <c r="F8" s="90" t="s">
+        <v>2054</v>
+      </c>
+      <c r="G8" s="90" t="s">
+        <v>2055</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="90" t="s">
+        <v>1989</v>
+      </c>
+      <c r="B9" s="90" t="s">
+        <v>1955</v>
+      </c>
+      <c r="C9" s="91" t="s">
+        <v>2035</v>
+      </c>
+      <c r="D9" s="90" t="s">
+        <v>12</v>
+      </c>
+      <c r="E9" s="90" t="s">
+        <v>2052</v>
+      </c>
+      <c r="F9" s="90" t="s">
+        <v>2054</v>
+      </c>
+      <c r="G9" s="90" t="s">
+        <v>2056</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="90" t="s">
+        <v>1990</v>
+      </c>
+      <c r="B10" s="90" t="s">
+        <v>1928</v>
+      </c>
+      <c r="C10" s="91" t="s">
+        <v>2036</v>
+      </c>
+      <c r="D10" s="90" t="s">
+        <v>12</v>
+      </c>
+      <c r="E10" s="90" t="s">
+        <v>2052</v>
+      </c>
+      <c r="F10" s="90" t="s">
+        <v>2054</v>
+      </c>
+      <c r="G10" s="90" t="s">
+        <v>2055</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="90" t="s">
+        <v>1991</v>
+      </c>
+      <c r="B11" s="90" t="s">
+        <v>2015</v>
+      </c>
+      <c r="C11" s="91" t="s">
+        <v>2037</v>
+      </c>
+      <c r="D11" s="90" t="s">
+        <v>18</v>
+      </c>
+      <c r="E11" s="90" t="s">
+        <v>2052</v>
+      </c>
+      <c r="F11" s="90" t="s">
+        <v>2054</v>
+      </c>
+      <c r="G11" s="90" t="s">
+        <v>2055</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="90" t="s">
+        <v>1992</v>
+      </c>
+      <c r="B12" s="90" t="s">
+        <v>22</v>
+      </c>
+      <c r="C12" s="91" t="s">
+        <v>2038</v>
+      </c>
+      <c r="D12" s="90" t="s">
+        <v>18</v>
+      </c>
+      <c r="E12" s="90" t="s">
+        <v>2052</v>
+      </c>
+      <c r="F12" s="90" t="s">
+        <v>2054</v>
+      </c>
+      <c r="G12" s="90" t="s">
+        <v>2055</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="90" t="s">
+        <v>1993</v>
+      </c>
+      <c r="B13" s="90" t="s">
+        <v>848</v>
+      </c>
+      <c r="C13" s="91" t="s">
+        <v>2039</v>
+      </c>
+      <c r="D13" s="90" t="s">
+        <v>18</v>
+      </c>
+      <c r="E13" s="90" t="s">
+        <v>2052</v>
+      </c>
+      <c r="F13" s="90" t="s">
+        <v>2054</v>
+      </c>
+      <c r="G13" s="90" t="s">
+        <v>2055</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="90" t="s">
+        <v>1994</v>
+      </c>
+      <c r="B14" s="90" t="s">
+        <v>2016</v>
+      </c>
+      <c r="C14" s="91" t="s">
+        <v>2040</v>
+      </c>
+      <c r="D14" s="90" t="s">
+        <v>866</v>
+      </c>
+      <c r="E14" s="90" t="s">
+        <v>2052</v>
+      </c>
+      <c r="F14" s="90" t="s">
+        <v>2054</v>
+      </c>
+      <c r="G14" s="90" t="s">
+        <v>2055</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="90" t="s">
+        <v>1995</v>
+      </c>
+      <c r="B15" s="90" t="s">
+        <v>2017</v>
+      </c>
+      <c r="C15" s="91" t="s">
+        <v>2041</v>
+      </c>
+      <c r="D15" s="90" t="s">
+        <v>1321</v>
+      </c>
+      <c r="E15" s="90" t="s">
+        <v>2053</v>
+      </c>
+      <c r="F15" s="90" t="s">
+        <v>2054</v>
+      </c>
+      <c r="G15" s="90" t="s">
+        <v>2055</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="90" t="s">
+        <v>1996</v>
+      </c>
+      <c r="B16" s="90" t="s">
+        <v>2018</v>
+      </c>
+      <c r="C16" s="91" t="s">
+        <v>2042</v>
+      </c>
+      <c r="D16" s="90" t="s">
+        <v>1321</v>
+      </c>
+      <c r="E16" s="90" t="s">
+        <v>2053</v>
+      </c>
+      <c r="F16" s="90" t="s">
+        <v>2054</v>
+      </c>
+      <c r="G16" s="90" t="s">
+        <v>2055</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="90" t="s">
+        <v>1997</v>
+      </c>
+      <c r="B17" s="90" t="s">
+        <v>921</v>
+      </c>
+      <c r="C17" s="91" t="s">
+        <v>2043</v>
+      </c>
+      <c r="D17" s="90" t="s">
+        <v>12</v>
+      </c>
+      <c r="E17" s="90" t="s">
+        <v>2053</v>
+      </c>
+      <c r="F17" s="90" t="s">
+        <v>2054</v>
+      </c>
+      <c r="G17" s="90" t="s">
+        <v>2055</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="90" t="s">
+        <v>1998</v>
+      </c>
+      <c r="B18" s="90" t="s">
+        <v>858</v>
+      </c>
+      <c r="C18" s="91" t="s">
+        <v>2044</v>
+      </c>
+      <c r="D18" s="90" t="s">
+        <v>12</v>
+      </c>
+      <c r="E18" s="90" t="s">
+        <v>2053</v>
+      </c>
+      <c r="F18" s="90" t="s">
+        <v>2054</v>
+      </c>
+      <c r="G18" s="90" t="s">
+        <v>2055</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="90" t="s">
+        <v>1999</v>
+      </c>
+      <c r="B19" s="90" t="s">
+        <v>245</v>
+      </c>
+      <c r="C19" s="91" t="s">
+        <v>2045</v>
+      </c>
+      <c r="D19" s="90" t="s">
+        <v>904</v>
+      </c>
+      <c r="E19" s="90" t="s">
+        <v>2053</v>
+      </c>
+      <c r="F19" s="90" t="s">
+        <v>2054</v>
+      </c>
+      <c r="G19" s="90" t="s">
+        <v>2055</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="90" t="s">
+        <v>2000</v>
+      </c>
+      <c r="B20" s="90" t="s">
+        <v>208</v>
+      </c>
+      <c r="C20" s="91" t="s">
+        <v>2045</v>
+      </c>
+      <c r="D20" s="90" t="s">
+        <v>16</v>
+      </c>
+      <c r="E20" s="90" t="s">
+        <v>2053</v>
+      </c>
+      <c r="F20" s="90" t="s">
+        <v>2054</v>
+      </c>
+      <c r="G20" s="90" t="s">
+        <v>2055</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="90" t="s">
+        <v>2001</v>
+      </c>
+      <c r="B21" s="90" t="s">
+        <v>2019</v>
+      </c>
+      <c r="C21" s="91" t="s">
+        <v>2046</v>
+      </c>
+      <c r="D21" s="90" t="s">
+        <v>26</v>
+      </c>
+      <c r="E21" s="90" t="s">
+        <v>2053</v>
+      </c>
+      <c r="F21" s="90" t="s">
+        <v>2054</v>
+      </c>
+      <c r="G21" s="90" t="s">
+        <v>2056</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="90" t="s">
+        <v>2002</v>
+      </c>
+      <c r="B22" s="90" t="s">
+        <v>2020</v>
+      </c>
+      <c r="C22" s="91" t="s">
+        <v>2046</v>
+      </c>
+      <c r="D22" s="90" t="s">
+        <v>26</v>
+      </c>
+      <c r="E22" s="90" t="s">
+        <v>2053</v>
+      </c>
+      <c r="F22" s="90" t="s">
+        <v>2054</v>
+      </c>
+      <c r="G22" s="90" t="s">
+        <v>2056</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="90" t="s">
+        <v>2003</v>
+      </c>
+      <c r="B23" s="90" t="s">
+        <v>2021</v>
+      </c>
+      <c r="C23" s="91" t="s">
+        <v>2046</v>
+      </c>
+      <c r="D23" s="90" t="s">
+        <v>1321</v>
+      </c>
+      <c r="E23" s="90" t="s">
+        <v>2053</v>
+      </c>
+      <c r="F23" s="90" t="s">
+        <v>2054</v>
+      </c>
+      <c r="G23" s="90" t="s">
+        <v>2056</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="90" t="s">
+        <v>2004</v>
+      </c>
+      <c r="B24" s="90" t="s">
+        <v>2022</v>
+      </c>
+      <c r="C24" s="91" t="s">
+        <v>2046</v>
+      </c>
+      <c r="D24" s="90" t="s">
+        <v>1321</v>
+      </c>
+      <c r="E24" s="90" t="s">
+        <v>2053</v>
+      </c>
+      <c r="F24" s="90" t="s">
+        <v>2054</v>
+      </c>
+      <c r="G24" s="90" t="s">
+        <v>2056</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="90" t="s">
+        <v>2005</v>
+      </c>
+      <c r="B25" s="90" t="s">
+        <v>2023</v>
+      </c>
+      <c r="C25" s="91" t="s">
+        <v>2046</v>
+      </c>
+      <c r="D25" s="90" t="s">
+        <v>1321</v>
+      </c>
+      <c r="E25" s="90" t="s">
+        <v>2053</v>
+      </c>
+      <c r="F25" s="90" t="s">
+        <v>2054</v>
+      </c>
+      <c r="G25" s="90" t="s">
+        <v>2056</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="90" t="s">
+        <v>2006</v>
+      </c>
+      <c r="B26" s="90" t="s">
+        <v>2024</v>
+      </c>
+      <c r="C26" s="91" t="s">
+        <v>2046</v>
+      </c>
+      <c r="D26" s="90" t="s">
+        <v>1321</v>
+      </c>
+      <c r="E26" s="90" t="s">
+        <v>2053</v>
+      </c>
+      <c r="F26" s="90" t="s">
+        <v>2054</v>
+      </c>
+      <c r="G26" s="90" t="s">
+        <v>2056</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="90" t="s">
+        <v>2007</v>
+      </c>
+      <c r="B27" s="90" t="s">
+        <v>2025</v>
+      </c>
+      <c r="C27" s="91" t="s">
+        <v>2046</v>
+      </c>
+      <c r="D27" s="90" t="s">
+        <v>1321</v>
+      </c>
+      <c r="E27" s="90" t="s">
+        <v>2053</v>
+      </c>
+      <c r="F27" s="90" t="s">
+        <v>2054</v>
+      </c>
+      <c r="G27" s="90" t="s">
+        <v>2056</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="90" t="s">
+        <v>2008</v>
+      </c>
+      <c r="B28" s="90" t="s">
+        <v>2026</v>
+      </c>
+      <c r="C28" s="91" t="s">
+        <v>2046</v>
+      </c>
+      <c r="D28" s="90" t="s">
+        <v>1321</v>
+      </c>
+      <c r="E28" s="90" t="s">
+        <v>2053</v>
+      </c>
+      <c r="F28" s="90" t="s">
+        <v>2054</v>
+      </c>
+      <c r="G28" s="90" t="s">
+        <v>2056</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="90" t="s">
+        <v>2009</v>
+      </c>
+      <c r="B29" s="90" t="s">
+        <v>2027</v>
+      </c>
+      <c r="C29" s="91" t="s">
+        <v>2047</v>
+      </c>
+      <c r="D29" s="90" t="s">
+        <v>2051</v>
+      </c>
+      <c r="E29" s="90" t="s">
+        <v>2053</v>
+      </c>
+      <c r="F29" s="90" t="s">
+        <v>2054</v>
+      </c>
+      <c r="G29" s="90" t="s">
+        <v>2055</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="90" t="s">
+        <v>2010</v>
+      </c>
+      <c r="B30" s="90" t="s">
+        <v>88</v>
+      </c>
+      <c r="C30" s="91" t="s">
+        <v>2048</v>
+      </c>
+      <c r="D30" s="90" t="s">
+        <v>866</v>
+      </c>
+      <c r="E30" s="90" t="s">
+        <v>2053</v>
+      </c>
+      <c r="F30" s="90" t="s">
+        <v>2054</v>
+      </c>
+      <c r="G30" s="90" t="s">
+        <v>2056</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="90" t="s">
+        <v>2011</v>
+      </c>
+      <c r="B31" s="90" t="s">
+        <v>94</v>
+      </c>
+      <c r="C31" s="91" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D31" s="90" t="s">
+        <v>16</v>
+      </c>
+      <c r="E31" s="90" t="s">
+        <v>2053</v>
+      </c>
+      <c r="F31" s="90" t="s">
+        <v>2054</v>
+      </c>
+      <c r="G31" s="90" t="s">
+        <v>2055</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="90" t="s">
+        <v>2012</v>
+      </c>
+      <c r="B32" s="91" t="s">
+        <v>153</v>
+      </c>
+      <c r="C32" s="91" t="s">
+        <v>2050</v>
+      </c>
+      <c r="D32" s="90" t="s">
+        <v>10</v>
+      </c>
+      <c r="E32" s="90" t="s">
+        <v>2053</v>
+      </c>
+      <c r="F32" s="90" t="s">
+        <v>2054</v>
+      </c>
+      <c r="G32" s="90" t="s">
+        <v>2055</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="90" verticalDpi="90" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5BE329E-0C32-C347-895C-9B9ADC4E5E27}">
   <dimension ref="A1:G456"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -18037,7 +19029,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8E4E2C6-ECF6-8E42-BACE-6A57540CDA47}">
   <dimension ref="A1:G348"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -26027,7 +27019,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3BB4C77-EC78-E54B-9F74-171DAF10810C}">
   <dimension ref="A1:G486"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -36924,13 +37916,13 @@
       <c r="A474" s="16" t="s">
         <v>1981</v>
       </c>
-      <c r="B474" s="90" t="s">
+      <c r="B474" s="75" t="s">
         <v>119</v>
       </c>
-      <c r="C474" s="91" t="s">
+      <c r="C474" s="4" t="s">
         <v>1407</v>
       </c>
-      <c r="D474" s="92" t="s">
+      <c r="D474" s="14" t="s">
         <v>14</v>
       </c>
       <c r="E474" t="s">

--- a/database.xlsx
+++ b/database.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/irione/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D8D98FC-A325-2645-A3FC-B4C0A8708C52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AD70F84-881D-5547-AB4C-A33F8A038983}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="11720" yWindow="600" windowWidth="23040" windowHeight="19380" xr2:uid="{6728D57D-078C-EB4A-903D-70A501F530A6}"/>
   </bookViews>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9226" uniqueCount="2057">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9226" uniqueCount="2056">
   <si>
     <t>GILDA FERNÁNDEZ VÁZQUEZ</t>
   </si>
@@ -6102,9 +6102,6 @@
   </si>
   <si>
     <t>PEDRO ANTONIO VELAZQUEZ VENTURA</t>
-  </si>
-  <si>
-    <t>IVÁN GONZÁLES LAZALDE</t>
   </si>
   <si>
     <t>MARIA LUISA ORTIZ PARGA</t>
@@ -7832,19 +7829,19 @@
         <v>33</v>
       </c>
       <c r="C2" s="91" t="s">
-        <v>2028</v>
+        <v>2027</v>
       </c>
       <c r="D2" s="90" t="s">
         <v>904</v>
       </c>
       <c r="E2" s="90" t="s">
-        <v>2052</v>
+        <v>2051</v>
       </c>
       <c r="F2" s="90" t="s">
+        <v>2053</v>
+      </c>
+      <c r="G2" s="90" t="s">
         <v>2054</v>
-      </c>
-      <c r="G2" s="90" t="s">
-        <v>2055</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -7855,19 +7852,19 @@
         <v>319</v>
       </c>
       <c r="C3" s="91" t="s">
-        <v>2029</v>
+        <v>2028</v>
       </c>
       <c r="D3" s="90" t="s">
         <v>16</v>
       </c>
       <c r="E3" s="90" t="s">
-        <v>2052</v>
+        <v>2051</v>
       </c>
       <c r="F3" s="90" t="s">
+        <v>2053</v>
+      </c>
+      <c r="G3" s="90" t="s">
         <v>2054</v>
-      </c>
-      <c r="G3" s="90" t="s">
-        <v>2055</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -7878,19 +7875,19 @@
         <v>2013</v>
       </c>
       <c r="C4" s="91" t="s">
-        <v>2030</v>
+        <v>2029</v>
       </c>
       <c r="D4" s="90" t="s">
         <v>10</v>
       </c>
       <c r="E4" s="90" t="s">
-        <v>2052</v>
+        <v>2051</v>
       </c>
       <c r="F4" s="90" t="s">
+        <v>2053</v>
+      </c>
+      <c r="G4" s="90" t="s">
         <v>2054</v>
-      </c>
-      <c r="G4" s="90" t="s">
-        <v>2055</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -7901,19 +7898,19 @@
         <v>1262</v>
       </c>
       <c r="C5" s="91" t="s">
-        <v>2031</v>
+        <v>2030</v>
       </c>
       <c r="D5" s="90" t="s">
         <v>7</v>
       </c>
       <c r="E5" s="90" t="s">
-        <v>2052</v>
+        <v>2051</v>
       </c>
       <c r="F5" s="90" t="s">
+        <v>2053</v>
+      </c>
+      <c r="G5" s="90" t="s">
         <v>2054</v>
-      </c>
-      <c r="G5" s="90" t="s">
-        <v>2055</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -7924,19 +7921,19 @@
         <v>2014</v>
       </c>
       <c r="C6" s="91" t="s">
-        <v>2032</v>
+        <v>2031</v>
       </c>
       <c r="D6" s="90" t="s">
         <v>7</v>
       </c>
       <c r="E6" s="90" t="s">
-        <v>2052</v>
+        <v>2051</v>
       </c>
       <c r="F6" s="90" t="s">
+        <v>2053</v>
+      </c>
+      <c r="G6" s="90" t="s">
         <v>2054</v>
-      </c>
-      <c r="G6" s="90" t="s">
-        <v>2055</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -7947,19 +7944,19 @@
         <v>850</v>
       </c>
       <c r="C7" s="91" t="s">
-        <v>2033</v>
+        <v>2032</v>
       </c>
       <c r="D7" s="90" t="s">
         <v>10</v>
       </c>
       <c r="E7" s="90" t="s">
-        <v>2052</v>
+        <v>2051</v>
       </c>
       <c r="F7" s="90" t="s">
+        <v>2053</v>
+      </c>
+      <c r="G7" s="90" t="s">
         <v>2054</v>
-      </c>
-      <c r="G7" s="90" t="s">
-        <v>2055</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -7970,19 +7967,19 @@
         <v>156</v>
       </c>
       <c r="C8" s="91" t="s">
-        <v>2034</v>
+        <v>2033</v>
       </c>
       <c r="D8" s="90" t="s">
         <v>866</v>
       </c>
       <c r="E8" s="90" t="s">
-        <v>2052</v>
+        <v>2051</v>
       </c>
       <c r="F8" s="90" t="s">
+        <v>2053</v>
+      </c>
+      <c r="G8" s="90" t="s">
         <v>2054</v>
-      </c>
-      <c r="G8" s="90" t="s">
-        <v>2055</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -7993,19 +7990,19 @@
         <v>1955</v>
       </c>
       <c r="C9" s="91" t="s">
-        <v>2035</v>
+        <v>2034</v>
       </c>
       <c r="D9" s="90" t="s">
         <v>12</v>
       </c>
       <c r="E9" s="90" t="s">
-        <v>2052</v>
+        <v>2051</v>
       </c>
       <c r="F9" s="90" t="s">
-        <v>2054</v>
+        <v>2053</v>
       </c>
       <c r="G9" s="90" t="s">
-        <v>2056</v>
+        <v>2055</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -8016,19 +8013,19 @@
         <v>1928</v>
       </c>
       <c r="C10" s="91" t="s">
-        <v>2036</v>
+        <v>2035</v>
       </c>
       <c r="D10" s="90" t="s">
         <v>12</v>
       </c>
       <c r="E10" s="90" t="s">
-        <v>2052</v>
+        <v>2051</v>
       </c>
       <c r="F10" s="90" t="s">
+        <v>2053</v>
+      </c>
+      <c r="G10" s="90" t="s">
         <v>2054</v>
-      </c>
-      <c r="G10" s="90" t="s">
-        <v>2055</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -8036,22 +8033,22 @@
         <v>1991</v>
       </c>
       <c r="B11" s="90" t="s">
-        <v>2015</v>
+        <v>849</v>
       </c>
       <c r="C11" s="91" t="s">
-        <v>2037</v>
+        <v>2036</v>
       </c>
       <c r="D11" s="90" t="s">
         <v>18</v>
       </c>
       <c r="E11" s="90" t="s">
-        <v>2052</v>
+        <v>2051</v>
       </c>
       <c r="F11" s="90" t="s">
+        <v>2053</v>
+      </c>
+      <c r="G11" s="90" t="s">
         <v>2054</v>
-      </c>
-      <c r="G11" s="90" t="s">
-        <v>2055</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -8062,19 +8059,19 @@
         <v>22</v>
       </c>
       <c r="C12" s="91" t="s">
-        <v>2038</v>
+        <v>2037</v>
       </c>
       <c r="D12" s="90" t="s">
         <v>18</v>
       </c>
       <c r="E12" s="90" t="s">
-        <v>2052</v>
+        <v>2051</v>
       </c>
       <c r="F12" s="90" t="s">
+        <v>2053</v>
+      </c>
+      <c r="G12" s="90" t="s">
         <v>2054</v>
-      </c>
-      <c r="G12" s="90" t="s">
-        <v>2055</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -8085,19 +8082,19 @@
         <v>848</v>
       </c>
       <c r="C13" s="91" t="s">
-        <v>2039</v>
+        <v>2038</v>
       </c>
       <c r="D13" s="90" t="s">
         <v>18</v>
       </c>
       <c r="E13" s="90" t="s">
-        <v>2052</v>
+        <v>2051</v>
       </c>
       <c r="F13" s="90" t="s">
+        <v>2053</v>
+      </c>
+      <c r="G13" s="90" t="s">
         <v>2054</v>
-      </c>
-      <c r="G13" s="90" t="s">
-        <v>2055</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -8105,22 +8102,22 @@
         <v>1994</v>
       </c>
       <c r="B14" s="90" t="s">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="C14" s="91" t="s">
-        <v>2040</v>
+        <v>2039</v>
       </c>
       <c r="D14" s="90" t="s">
         <v>866</v>
       </c>
       <c r="E14" s="90" t="s">
-        <v>2052</v>
+        <v>2051</v>
       </c>
       <c r="F14" s="90" t="s">
+        <v>2053</v>
+      </c>
+      <c r="G14" s="90" t="s">
         <v>2054</v>
-      </c>
-      <c r="G14" s="90" t="s">
-        <v>2055</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -8128,22 +8125,22 @@
         <v>1995</v>
       </c>
       <c r="B15" s="90" t="s">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="C15" s="91" t="s">
-        <v>2041</v>
+        <v>2040</v>
       </c>
       <c r="D15" s="90" t="s">
         <v>1321</v>
       </c>
       <c r="E15" s="90" t="s">
+        <v>2052</v>
+      </c>
+      <c r="F15" s="90" t="s">
         <v>2053</v>
       </c>
-      <c r="F15" s="90" t="s">
+      <c r="G15" s="90" t="s">
         <v>2054</v>
-      </c>
-      <c r="G15" s="90" t="s">
-        <v>2055</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -8151,22 +8148,22 @@
         <v>1996</v>
       </c>
       <c r="B16" s="90" t="s">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="C16" s="91" t="s">
-        <v>2042</v>
+        <v>2041</v>
       </c>
       <c r="D16" s="90" t="s">
         <v>1321</v>
       </c>
       <c r="E16" s="90" t="s">
+        <v>2052</v>
+      </c>
+      <c r="F16" s="90" t="s">
         <v>2053</v>
       </c>
-      <c r="F16" s="90" t="s">
+      <c r="G16" s="90" t="s">
         <v>2054</v>
-      </c>
-      <c r="G16" s="90" t="s">
-        <v>2055</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -8177,19 +8174,19 @@
         <v>921</v>
       </c>
       <c r="C17" s="91" t="s">
-        <v>2043</v>
+        <v>2042</v>
       </c>
       <c r="D17" s="90" t="s">
         <v>12</v>
       </c>
       <c r="E17" s="90" t="s">
+        <v>2052</v>
+      </c>
+      <c r="F17" s="90" t="s">
         <v>2053</v>
       </c>
-      <c r="F17" s="90" t="s">
+      <c r="G17" s="90" t="s">
         <v>2054</v>
-      </c>
-      <c r="G17" s="90" t="s">
-        <v>2055</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -8200,19 +8197,19 @@
         <v>858</v>
       </c>
       <c r="C18" s="91" t="s">
-        <v>2044</v>
+        <v>2043</v>
       </c>
       <c r="D18" s="90" t="s">
         <v>12</v>
       </c>
       <c r="E18" s="90" t="s">
+        <v>2052</v>
+      </c>
+      <c r="F18" s="90" t="s">
         <v>2053</v>
       </c>
-      <c r="F18" s="90" t="s">
+      <c r="G18" s="90" t="s">
         <v>2054</v>
-      </c>
-      <c r="G18" s="90" t="s">
-        <v>2055</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -8223,19 +8220,19 @@
         <v>245</v>
       </c>
       <c r="C19" s="91" t="s">
-        <v>2045</v>
+        <v>2044</v>
       </c>
       <c r="D19" s="90" t="s">
         <v>904</v>
       </c>
       <c r="E19" s="90" t="s">
+        <v>2052</v>
+      </c>
+      <c r="F19" s="90" t="s">
         <v>2053</v>
       </c>
-      <c r="F19" s="90" t="s">
+      <c r="G19" s="90" t="s">
         <v>2054</v>
-      </c>
-      <c r="G19" s="90" t="s">
-        <v>2055</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -8246,19 +8243,19 @@
         <v>208</v>
       </c>
       <c r="C20" s="91" t="s">
-        <v>2045</v>
+        <v>2044</v>
       </c>
       <c r="D20" s="90" t="s">
         <v>16</v>
       </c>
       <c r="E20" s="90" t="s">
+        <v>2052</v>
+      </c>
+      <c r="F20" s="90" t="s">
         <v>2053</v>
       </c>
-      <c r="F20" s="90" t="s">
+      <c r="G20" s="90" t="s">
         <v>2054</v>
-      </c>
-      <c r="G20" s="90" t="s">
-        <v>2055</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -8266,22 +8263,22 @@
         <v>2001</v>
       </c>
       <c r="B21" s="90" t="s">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="C21" s="91" t="s">
-        <v>2046</v>
+        <v>2045</v>
       </c>
       <c r="D21" s="90" t="s">
         <v>26</v>
       </c>
       <c r="E21" s="90" t="s">
+        <v>2052</v>
+      </c>
+      <c r="F21" s="90" t="s">
         <v>2053</v>
       </c>
-      <c r="F21" s="90" t="s">
-        <v>2054</v>
-      </c>
       <c r="G21" s="90" t="s">
-        <v>2056</v>
+        <v>2055</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -8289,22 +8286,22 @@
         <v>2002</v>
       </c>
       <c r="B22" s="90" t="s">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C22" s="91" t="s">
-        <v>2046</v>
+        <v>2045</v>
       </c>
       <c r="D22" s="90" t="s">
         <v>26</v>
       </c>
       <c r="E22" s="90" t="s">
+        <v>2052</v>
+      </c>
+      <c r="F22" s="90" t="s">
         <v>2053</v>
       </c>
-      <c r="F22" s="90" t="s">
-        <v>2054</v>
-      </c>
       <c r="G22" s="90" t="s">
-        <v>2056</v>
+        <v>2055</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -8312,22 +8309,22 @@
         <v>2003</v>
       </c>
       <c r="B23" s="90" t="s">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C23" s="91" t="s">
-        <v>2046</v>
+        <v>2045</v>
       </c>
       <c r="D23" s="90" t="s">
         <v>1321</v>
       </c>
       <c r="E23" s="90" t="s">
+        <v>2052</v>
+      </c>
+      <c r="F23" s="90" t="s">
         <v>2053</v>
       </c>
-      <c r="F23" s="90" t="s">
-        <v>2054</v>
-      </c>
       <c r="G23" s="90" t="s">
-        <v>2056</v>
+        <v>2055</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -8335,22 +8332,22 @@
         <v>2004</v>
       </c>
       <c r="B24" s="90" t="s">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C24" s="91" t="s">
-        <v>2046</v>
+        <v>2045</v>
       </c>
       <c r="D24" s="90" t="s">
         <v>1321</v>
       </c>
       <c r="E24" s="90" t="s">
+        <v>2052</v>
+      </c>
+      <c r="F24" s="90" t="s">
         <v>2053</v>
       </c>
-      <c r="F24" s="90" t="s">
-        <v>2054</v>
-      </c>
       <c r="G24" s="90" t="s">
-        <v>2056</v>
+        <v>2055</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -8358,22 +8355,22 @@
         <v>2005</v>
       </c>
       <c r="B25" s="90" t="s">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C25" s="91" t="s">
-        <v>2046</v>
+        <v>2045</v>
       </c>
       <c r="D25" s="90" t="s">
         <v>1321</v>
       </c>
       <c r="E25" s="90" t="s">
+        <v>2052</v>
+      </c>
+      <c r="F25" s="90" t="s">
         <v>2053</v>
       </c>
-      <c r="F25" s="90" t="s">
-        <v>2054</v>
-      </c>
       <c r="G25" s="90" t="s">
-        <v>2056</v>
+        <v>2055</v>
       </c>
     </row>
     <row r="26" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -8381,22 +8378,22 @@
         <v>2006</v>
       </c>
       <c r="B26" s="90" t="s">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C26" s="91" t="s">
-        <v>2046</v>
+        <v>2045</v>
       </c>
       <c r="D26" s="90" t="s">
         <v>1321</v>
       </c>
       <c r="E26" s="90" t="s">
+        <v>2052</v>
+      </c>
+      <c r="F26" s="90" t="s">
         <v>2053</v>
       </c>
-      <c r="F26" s="90" t="s">
-        <v>2054</v>
-      </c>
       <c r="G26" s="90" t="s">
-        <v>2056</v>
+        <v>2055</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -8404,22 +8401,22 @@
         <v>2007</v>
       </c>
       <c r="B27" s="90" t="s">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C27" s="91" t="s">
-        <v>2046</v>
+        <v>2045</v>
       </c>
       <c r="D27" s="90" t="s">
         <v>1321</v>
       </c>
       <c r="E27" s="90" t="s">
+        <v>2052</v>
+      </c>
+      <c r="F27" s="90" t="s">
         <v>2053</v>
       </c>
-      <c r="F27" s="90" t="s">
-        <v>2054</v>
-      </c>
       <c r="G27" s="90" t="s">
-        <v>2056</v>
+        <v>2055</v>
       </c>
     </row>
     <row r="28" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -8427,22 +8424,22 @@
         <v>2008</v>
       </c>
       <c r="B28" s="90" t="s">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C28" s="91" t="s">
-        <v>2046</v>
+        <v>2045</v>
       </c>
       <c r="D28" s="90" t="s">
         <v>1321</v>
       </c>
       <c r="E28" s="90" t="s">
+        <v>2052</v>
+      </c>
+      <c r="F28" s="90" t="s">
         <v>2053</v>
       </c>
-      <c r="F28" s="90" t="s">
-        <v>2054</v>
-      </c>
       <c r="G28" s="90" t="s">
-        <v>2056</v>
+        <v>2055</v>
       </c>
     </row>
     <row r="29" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -8450,22 +8447,22 @@
         <v>2009</v>
       </c>
       <c r="B29" s="90" t="s">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="C29" s="91" t="s">
-        <v>2047</v>
+        <v>2046</v>
       </c>
       <c r="D29" s="90" t="s">
-        <v>2051</v>
+        <v>2050</v>
       </c>
       <c r="E29" s="90" t="s">
+        <v>2052</v>
+      </c>
+      <c r="F29" s="90" t="s">
         <v>2053</v>
       </c>
-      <c r="F29" s="90" t="s">
+      <c r="G29" s="90" t="s">
         <v>2054</v>
-      </c>
-      <c r="G29" s="90" t="s">
-        <v>2055</v>
       </c>
     </row>
     <row r="30" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -8476,19 +8473,19 @@
         <v>88</v>
       </c>
       <c r="C30" s="91" t="s">
-        <v>2048</v>
+        <v>2047</v>
       </c>
       <c r="D30" s="90" t="s">
         <v>866</v>
       </c>
       <c r="E30" s="90" t="s">
+        <v>2052</v>
+      </c>
+      <c r="F30" s="90" t="s">
         <v>2053</v>
       </c>
-      <c r="F30" s="90" t="s">
-        <v>2054</v>
-      </c>
       <c r="G30" s="90" t="s">
-        <v>2056</v>
+        <v>2055</v>
       </c>
     </row>
     <row r="31" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -8499,19 +8496,19 @@
         <v>94</v>
       </c>
       <c r="C31" s="91" t="s">
-        <v>2049</v>
+        <v>2048</v>
       </c>
       <c r="D31" s="90" t="s">
         <v>16</v>
       </c>
       <c r="E31" s="90" t="s">
+        <v>2052</v>
+      </c>
+      <c r="F31" s="90" t="s">
         <v>2053</v>
       </c>
-      <c r="F31" s="90" t="s">
+      <c r="G31" s="90" t="s">
         <v>2054</v>
-      </c>
-      <c r="G31" s="90" t="s">
-        <v>2055</v>
       </c>
     </row>
     <row r="32" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -8522,19 +8519,19 @@
         <v>153</v>
       </c>
       <c r="C32" s="91" t="s">
-        <v>2050</v>
+        <v>2049</v>
       </c>
       <c r="D32" s="90" t="s">
         <v>10</v>
       </c>
       <c r="E32" s="90" t="s">
+        <v>2052</v>
+      </c>
+      <c r="F32" s="90" t="s">
         <v>2053</v>
       </c>
-      <c r="F32" s="90" t="s">
+      <c r="G32" s="90" t="s">
         <v>2054</v>
-      </c>
-      <c r="G32" s="90" t="s">
-        <v>2055</v>
       </c>
     </row>
   </sheetData>

--- a/database.xlsx
+++ b/database.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/irione/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B02E7F49-19EE-BC43-83A1-91A64FCA754D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A784C735-704A-844A-AA8F-1A23A63EC5F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4760" yWindow="600" windowWidth="27240" windowHeight="16160" xr2:uid="{6728D57D-078C-EB4A-903D-70A501F530A6}"/>
   </bookViews>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11900" uniqueCount="2492">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11900" uniqueCount="2493">
   <si>
     <t>GILDA FERNÁNDEZ VÁZQUEZ</t>
   </si>
@@ -7533,6 +7533,9 @@
   </si>
   <si>
     <t>POSGRADO E INVESTIGACION</t>
+  </si>
+  <si>
+    <t>SIMULACIÓN CON PROMODEL</t>
   </si>
 </sst>
 </file>
@@ -13211,7 +13214,7 @@
         <v>40</v>
       </c>
       <c r="C179" s="90" t="s">
-        <v>2038</v>
+        <v>2492</v>
       </c>
       <c r="D179" s="90" t="s">
         <v>2486</v>
@@ -13234,7 +13237,7 @@
         <v>38</v>
       </c>
       <c r="C180" s="90" t="s">
-        <v>2038</v>
+        <v>2492</v>
       </c>
       <c r="D180" s="90" t="s">
         <v>2486</v>
@@ -13257,7 +13260,7 @@
         <v>44</v>
       </c>
       <c r="C181" s="90" t="s">
-        <v>2038</v>
+        <v>2492</v>
       </c>
       <c r="D181" s="90" t="s">
         <v>2486</v>
@@ -13280,7 +13283,7 @@
         <v>68</v>
       </c>
       <c r="C182" s="90" t="s">
-        <v>2038</v>
+        <v>2492</v>
       </c>
       <c r="D182" s="90" t="s">
         <v>2486</v>
@@ -13303,7 +13306,7 @@
         <v>70</v>
       </c>
       <c r="C183" s="90" t="s">
-        <v>2038</v>
+        <v>2492</v>
       </c>
       <c r="D183" s="90" t="s">
         <v>2486</v>
@@ -13326,7 +13329,7 @@
         <v>42</v>
       </c>
       <c r="C184" s="90" t="s">
-        <v>2038</v>
+        <v>2492</v>
       </c>
       <c r="D184" s="90" t="s">
         <v>2486</v>
@@ -13349,7 +13352,7 @@
         <v>74</v>
       </c>
       <c r="C185" s="90" t="s">
-        <v>2038</v>
+        <v>2492</v>
       </c>
       <c r="D185" s="90" t="s">
         <v>2486</v>
@@ -13372,7 +13375,7 @@
         <v>60</v>
       </c>
       <c r="C186" s="90" t="s">
-        <v>2038</v>
+        <v>2492</v>
       </c>
       <c r="D186" s="90" t="s">
         <v>2486</v>
@@ -13395,7 +13398,7 @@
         <v>58</v>
       </c>
       <c r="C187" s="90" t="s">
-        <v>2038</v>
+        <v>2492</v>
       </c>
       <c r="D187" s="90" t="s">
         <v>2486</v>
@@ -13418,7 +13421,7 @@
         <v>64</v>
       </c>
       <c r="C188" s="90" t="s">
-        <v>2038</v>
+        <v>2492</v>
       </c>
       <c r="D188" s="90" t="s">
         <v>2486</v>
@@ -13441,7 +13444,7 @@
         <v>244</v>
       </c>
       <c r="C189" s="90" t="s">
-        <v>2038</v>
+        <v>2492</v>
       </c>
       <c r="D189" s="90" t="s">
         <v>2486</v>
@@ -13464,7 +13467,7 @@
         <v>27</v>
       </c>
       <c r="C190" s="90" t="s">
-        <v>2038</v>
+        <v>2492</v>
       </c>
       <c r="D190" s="90" t="s">
         <v>2486</v>
@@ -13487,7 +13490,7 @@
         <v>1285</v>
       </c>
       <c r="C191" s="90" t="s">
-        <v>2038</v>
+        <v>2492</v>
       </c>
       <c r="D191" s="90" t="s">
         <v>2486</v>
@@ -13510,7 +13513,7 @@
         <v>52</v>
       </c>
       <c r="C192" s="90" t="s">
-        <v>2038</v>
+        <v>2492</v>
       </c>
       <c r="D192" s="90" t="s">
         <v>2486</v>
@@ -13533,7 +13536,7 @@
         <v>230</v>
       </c>
       <c r="C193" s="90" t="s">
-        <v>2038</v>
+        <v>2492</v>
       </c>
       <c r="D193" s="90" t="s">
         <v>2486</v>
@@ -13556,7 +13559,7 @@
         <v>355</v>
       </c>
       <c r="C194" s="90" t="s">
-        <v>2038</v>
+        <v>2492</v>
       </c>
       <c r="D194" s="90" t="s">
         <v>2486</v>
@@ -13579,7 +13582,7 @@
         <v>1901</v>
       </c>
       <c r="C195" s="90" t="s">
-        <v>2038</v>
+        <v>2492</v>
       </c>
       <c r="D195" s="90" t="s">
         <v>2488</v>

--- a/database.xlsx
+++ b/database.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/irione/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A784C735-704A-844A-AA8F-1A23A63EC5F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71D3C147-4712-1544-85B5-8072F4C85377}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4760" yWindow="600" windowWidth="27240" windowHeight="16160" xr2:uid="{6728D57D-078C-EB4A-903D-70A501F530A6}"/>
   </bookViews>
@@ -18366,7 +18366,7 @@
         <v>1281</v>
       </c>
       <c r="C403" s="90" t="s">
-        <v>2047</v>
+        <v>2482</v>
       </c>
       <c r="D403" s="90" t="s">
         <v>2490</v>
@@ -18389,7 +18389,7 @@
         <v>156</v>
       </c>
       <c r="C404" s="90" t="s">
-        <v>2047</v>
+        <v>2482</v>
       </c>
       <c r="D404" s="90" t="s">
         <v>2490</v>
@@ -18412,7 +18412,7 @@
         <v>105</v>
       </c>
       <c r="C405" s="90" t="s">
-        <v>2047</v>
+        <v>2482</v>
       </c>
       <c r="D405" s="90" t="s">
         <v>2490</v>
@@ -18435,7 +18435,7 @@
         <v>1306</v>
       </c>
       <c r="C406" s="90" t="s">
-        <v>2047</v>
+        <v>2482</v>
       </c>
       <c r="D406" s="90" t="s">
         <v>2490</v>
@@ -18458,7 +18458,7 @@
         <v>1280</v>
       </c>
       <c r="C407" s="90" t="s">
-        <v>2047</v>
+        <v>2482</v>
       </c>
       <c r="D407" s="90" t="s">
         <v>2490</v>
@@ -18481,7 +18481,7 @@
         <v>850</v>
       </c>
       <c r="C408" s="90" t="s">
-        <v>2047</v>
+        <v>2482</v>
       </c>
       <c r="D408" s="90" t="s">
         <v>2490</v>
@@ -18504,7 +18504,7 @@
         <v>263</v>
       </c>
       <c r="C409" s="90" t="s">
-        <v>2047</v>
+        <v>2482</v>
       </c>
       <c r="D409" s="90" t="s">
         <v>2490</v>
@@ -18527,7 +18527,7 @@
         <v>1239</v>
       </c>
       <c r="C410" s="90" t="s">
-        <v>2047</v>
+        <v>2482</v>
       </c>
       <c r="D410" s="90" t="s">
         <v>2490</v>
@@ -18550,7 +18550,7 @@
         <v>2481</v>
       </c>
       <c r="C411" s="90" t="s">
-        <v>2047</v>
+        <v>2482</v>
       </c>
       <c r="D411" s="90" t="s">
         <v>2490</v>
@@ -18573,7 +18573,7 @@
         <v>2460</v>
       </c>
       <c r="C412" s="90" t="s">
-        <v>2047</v>
+        <v>2482</v>
       </c>
       <c r="D412" s="90" t="s">
         <v>2490</v>
@@ -18596,7 +18596,7 @@
         <v>261</v>
       </c>
       <c r="C413" s="90" t="s">
-        <v>2047</v>
+        <v>2482</v>
       </c>
       <c r="D413" s="94" t="s">
         <v>2490</v>
@@ -18619,7 +18619,7 @@
         <v>118</v>
       </c>
       <c r="C414" s="90" t="s">
-        <v>2047</v>
+        <v>2482</v>
       </c>
       <c r="D414" s="94" t="s">
         <v>2490</v>
